--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260731.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.76%</t>
+          <t>28.81%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.26%</t>
+          <t>8.31%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.96%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>5.68%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.12%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1012,73 +1012,73 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>89,356,605</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>23,698</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>141,205</t>
+          <t>23,698</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1107,110 +1107,110 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>20,515</t>
+          <t>141,205</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,566</t>
+          <t>20,515</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>66,944,471</t>
+          <t>10,566</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,984,130</t>
+          <t>17,671</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>17,671</t>
+          <t>13,105</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1232,95 +1232,73 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,105</t>
+          <t>48,100</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>48,100</t>
+          <t>21,687</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>21,687</t>
+          <t>984,130</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>32,377,000</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
